--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,7 +404,7 @@
     <t>MOS ANS / TRE_R09-CategorieProfessionnelle</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-practitioner-role-categorie-professionnelle</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-categorie-professionnelle</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -779,7 +779,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="42.9453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.30078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="80.67578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-role-code-categorie-professionnelle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
